--- a/healthcare_forms/017_perimenopause_quiz--healthcare_forms.xlsx
+++ b/healthcare_forms/017_perimenopause_quiz--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>perimenopause_quiz_form_additional_comments</t>
+          <t>perimenopause_quiz_form_additional_comments_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>Perimenopause Quiz Form Additional Comments 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>perimenopause_quiz_form_menopause_symptoms_duration</t>
+          <t>perimenopause_quiz_form_menopause_symptoms_duration_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Duration of Symptoms</t>
+          <t>Perimenopause Quiz Form Menopause Symptoms Duration 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Frequency of Symptoms</t>
+          <t>Perimenopause Quiz Form Menopause Symptoms Frequency 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Severity of Symptoms</t>
+          <t>Perimenopause Quiz Form Menopause Symptoms Severity 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Timing of Symptoms</t>
+          <t>Perimenopause Quiz Form Menopause Symptoms Timing 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Onset of Symptoms</t>
+          <t>Perimenopause Quiz Form Menopause Symptoms Onset 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>perimenopause_quiz_form_menopause_symptoms_duration_2</t>
+          <t>perimenopause_quiz_form_menopause_symptoms_duration_2_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Duration of Symptoms</t>
+          <t>Perimenopause Quiz Form Menopause Symptoms Duration 2 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1010,8 +1010,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'menstrual_cycle_irregularity'}</t>
+          <t>menstrual_cycle_irregularity</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Menstrual cycle irregularity'}</t>
+          <t>Menstrual cycle irregularity</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'menstrual_cycle_regularity'}</t>
+          <t>menstrual_cycle_regularity</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Menstrual cycle regularity'}</t>
+          <t>Menstrual cycle regularity</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'postmenstrual_bleeding'}</t>
+          <t>postmenstrual_bleeding</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Postmenstrual bleeding'}</t>
+          <t>Postmenstrual bleeding</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'vaginal_dryness'}</t>
+          <t>vaginal_dryness</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Vaginal dryness'}</t>
+          <t>Vaginal dryness</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'hot_flashes'}</t>
+          <t>hot_flashes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Hot flashes'}</t>
+          <t>Hot flashes</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'night_sweats'}</t>
+          <t>night_sweats</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Night sweats'}</t>
+          <t>Night sweats</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'mood_changes'}</t>
+          <t>mood_changes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Mood changes'}</t>
+          <t>Mood changes</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'weight_changes'}</t>
+          <t>weight_changes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Weight changes'}</t>
+          <t>Weight changes</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'hot_flashes'}</t>
+          <t>hot_flashes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Hot flashes'}</t>
+          <t>Hot flashes</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'night_sweats'}</t>
+          <t>night_sweats</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Night sweats'}</t>
+          <t>Night sweats</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'vaginal_dryness'}</t>
+          <t>vaginal_dryness</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Vaginal dryness'}</t>
+          <t>Vaginal dryness</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'mood_changes'}</t>
+          <t>mood_changes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Mood changes'}</t>
+          <t>Mood changes</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'weight_changes'}</t>
+          <t>weight_changes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Weight changes'}</t>
+          <t>Weight changes</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'loss_of_sex_drive'}</t>
+          <t>loss_of_sex_drive</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Loss of sex drive'}</t>
+          <t>Loss of sex drive</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'sleep_disturbances'}</t>
+          <t>sleep_disturbances</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Sleep disturbances'}</t>
+          <t>Sleep disturbances</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'forgetfulness'}</t>
+          <t>forgetfulness</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Forgetfulness'}</t>
+          <t>Forgetfulness</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'reduced_risk_of_ovarian_cancer'}</t>
+          <t>reduced_risk_of_ovarian_cancer</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Reduced risk of ovarian cancer'}</t>
+          <t>Reduced risk of ovarian cancer</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'reduced_risk_of_endometrial_cancer'}</t>
+          <t>reduced_risk_of_endometrial_cancer</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Reduced risk of endometrial cancer'}</t>
+          <t>Reduced risk of endometrial cancer</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'increased_self-esteem'}</t>
+          <t>increased_self-esteem</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Increased self-esteem'}</t>
+          <t>Increased self-esteem</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'improved_mental_health'}</t>
+          <t>improved_mental_health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Improved mental health'}</t>
+          <t>Improved mental health</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'increased_sense_of_calmness'}</t>
+          <t>increased_sense_of_calmness</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Increased sense of calmness'}</t>
+          <t>Increased sense of calmness</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'improved_sleep'}</t>
+          <t>improved_sleep</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Improved sleep'}</t>
+          <t>Improved sleep</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'better_body_image'}</t>
+          <t>better_body_image</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Better body image'}</t>
+          <t>Better body image</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'reduced_risk_of_osteoporosis'}</t>
+          <t>reduced_risk_of_osteoporosis</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Reduced risk of osteoporosis'}</t>
+          <t>Reduced risk of osteoporosis</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
